--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -48671,7 +48671,7 @@
         <v>46275</v>
       </c>
       <c r="K616" s="2">
-        <v>46305</v>
+        <v>46275</v>
       </c>
       <c r="L616">
         <v>1</v>
@@ -48680,16 +48680,16 @@
         <v>1295</v>
       </c>
       <c r="N616" s="2">
-        <v>46312</v>
+        <v>46282</v>
       </c>
       <c r="O616" s="2">
         <v>46282</v>
       </c>
       <c r="Q616">
-        <v>-32</v>
+        <v>-2</v>
       </c>
       <c r="R616">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="S616" t="s">
         <v>1542</v>
@@ -48742,7 +48742,7 @@
         <v>46275</v>
       </c>
       <c r="K617" s="2">
-        <v>46305</v>
+        <v>46275</v>
       </c>
       <c r="L617">
         <v>1</v>
@@ -48751,16 +48751,16 @@
         <v>1295</v>
       </c>
       <c r="N617" s="2">
-        <v>46312</v>
+        <v>46282</v>
       </c>
       <c r="O617" s="2">
         <v>46282</v>
       </c>
       <c r="Q617">
-        <v>-32</v>
+        <v>-2</v>
       </c>
       <c r="R617">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="S617" t="s">
         <v>1542</v>
@@ -48813,7 +48813,7 @@
         <v>46275</v>
       </c>
       <c r="K618" s="2">
-        <v>46305</v>
+        <v>46275</v>
       </c>
       <c r="L618">
         <v>1</v>
@@ -48822,13 +48822,13 @@
         <v>1295</v>
       </c>
       <c r="N618" s="2">
-        <v>46316</v>
+        <v>46286</v>
       </c>
       <c r="Q618">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="R618">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="S618" t="s">
         <v>1542</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -46677,10 +46677,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R586">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S586" t="s">
         <v>1558</v>
@@ -47561,10 +47561,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R599">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S599" t="s">
         <v>1558</v>
@@ -47694,10 +47694,10 @@
         <v>46294</v>
       </c>
       <c r="Q601">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R601">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S601" t="s">
         <v>1558</v>
@@ -47830,10 +47830,10 @@
         <v>46258</v>
       </c>
       <c r="Q603">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R603">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S603" t="s">
         <v>1558</v>
@@ -48448,10 +48448,10 @@
         <v>1553</v>
       </c>
       <c r="Q612">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R612">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S612" t="s">
         <v>1559</v>
@@ -48933,10 +48933,10 @@
         <v>1556</v>
       </c>
       <c r="Q619">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S619" t="s">
         <v>1559</v>
@@ -49078,10 +49078,10 @@
         <v>46288</v>
       </c>
       <c r="Q621">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S621" t="s">
         <v>1558</v>
@@ -49149,10 +49149,10 @@
         <v>46288</v>
       </c>
       <c r="Q622">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S622" t="s">
         <v>1558</v>
@@ -49220,10 +49220,10 @@
         <v>46288</v>
       </c>
       <c r="Q623">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S623" t="s">
         <v>1558</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8188" uniqueCount="2508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8192" uniqueCount="2509">
   <si>
     <t>om_emg</t>
   </si>
@@ -6343,7 +6343,7 @@
     <t>Operador pediu para fornecer o PN informado. Godoy 18/09/26. AWB 12758218764 -  volume retirado na loja GOLLOG - NAT por teodoro silva no dia 21/09. Godoy 22/09/26.  Item atendido pela NF 2227 em 22/09/2026. Godoy 24/09/2026.</t>
   </si>
   <si>
-    <t>AWB 12759588944 - volume retirado na loja GOLLOG - NAT por teodoro silva em 25/09. Godoy 06/10/26.</t>
+    <t>AWB 12759588944 - volume retirado na loja GOLLOG - NAT por teodoro silva em 25/09. Godoy 06/10/26. Informado recibo 822/FAB/26 porém PN atendido não consta como alternado do PN em emergência. Ramon 08/10/26.</t>
   </si>
   <si>
     <t>será atendido pelo estoque FAB pedido n° 18422910. Godoy 16/09/26</t>
@@ -6367,7 +6367,7 @@
     <t>Emerg será atendida pelo estoque FAB pedido 18540739. Godoy 29/09. Recebido por SO Ferreira no dia 01/10. Godoy 02/10/26.</t>
   </si>
   <si>
-    <t>AWB 12760704954 - volume retirado na loja GOLLOG - BSB por Kesia de Sousa. Godoy 06/10/2026</t>
+    <t>AWB 12760704954 - volume retirado na loja GOLLOG - BSB por 3S Kesia de Sousa. Godoy 06/10/2026</t>
   </si>
   <si>
     <t>Emerg será atendida pelo estoque FAB pedido 18553814. Godoy 30/09. Recebido por 2S Olegario no dia 02/10/26. Godoy 05/10/26</t>
@@ -6391,15 +6391,15 @@
     <t>Emerg. cancelada pelo operador. Godoy 07/10/26</t>
   </si>
   <si>
+    <t>Atendido com esoque local em 08/10. Ramon 08/10/26.</t>
+  </si>
+  <si>
     <t>ESTE ITEM FOI ENVIADO POR ENGANO PARA BAMN. ESTAMOS RESGATANDO O ITEM PARA ENVIAR DE VOLTA AO FORNECEDOR PARA QUE ELE NOS ENVIE O ITEM CORRETO.</t>
   </si>
   <si>
     <t>Colocado pedido Textron IJ17740209 - tracking 539575366041 - previsão de entrega V1 RJ 23/09 - MATERIAL ENVIADO VIA RECIBO 822/FAB/26 AWB 12759588944 DPE 25/09/2026 - MATERIAL JÁ ENTREGUE NO SUPRIMENTOS BANT DIA 25/09/2026</t>
   </si>
   <si>
-    <t>ENVIADO DI A 30-09-26 AWB 127-6046 3314 - CLA-01-10</t>
-  </si>
-  <si>
     <t>Colocado pedido Textron WB0003167445 - tracking 542505808925 - previsão de entrega V1 RJ 01/10 - MATERIAL ENVIADO PELA AWB 12761197990 dpe 08/10/2026</t>
   </si>
   <si>
@@ -6412,10 +6412,13 @@
     <t>RECEBIDO 01 EA, REPARADO , DA WILLIAM EM 05/10/26. SERÁ ATD ESTA EMERG - REZ (06/10/26)</t>
   </si>
   <si>
+    <t>Item ainda em pesquisa de pane pelo CLA. Não confirmaram a pane como COMPRESSOR. SO R1 BISPO 07/10/26</t>
+  </si>
+  <si>
     <t>DPE 09/10/26 - REZ(06-10-26), email solicitando abertura de o.s. dia 30-09-26, CLA -06-10-26</t>
   </si>
   <si>
-    <t>MATERIAL ENVIADO PELA AWB 12760678343, RETIRADO DIA 05/10/2026</t>
+    <t>Em cotação no mercado. ATZ 07/10</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -8015,7 +8018,7 @@
         <v>1617</v>
       </c>
       <c r="W2" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -8077,16 +8080,16 @@
         <v>1618</v>
       </c>
       <c r="W3" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X3" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="Y3" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z3" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -8148,7 +8151,7 @@
         <v>1617</v>
       </c>
       <c r="W4" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -8210,7 +8213,7 @@
         <v>1619</v>
       </c>
       <c r="W5" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -8272,7 +8275,7 @@
         <v>1620</v>
       </c>
       <c r="W6" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -8334,7 +8337,7 @@
         <v>1621</v>
       </c>
       <c r="W7" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -8396,7 +8399,7 @@
         <v>1622</v>
       </c>
       <c r="W8" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -8458,7 +8461,7 @@
         <v>1623</v>
       </c>
       <c r="W9" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8520,7 +8523,7 @@
         <v>1624</v>
       </c>
       <c r="W10" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8582,7 +8585,7 @@
         <v>1625</v>
       </c>
       <c r="W11" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8644,7 +8647,7 @@
         <v>1626</v>
       </c>
       <c r="W12" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8706,7 +8709,7 @@
         <v>1622</v>
       </c>
       <c r="W13" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8768,16 +8771,16 @@
         <v>1627</v>
       </c>
       <c r="W14" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X14" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="Y14" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z14" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8836,7 +8839,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8901,7 +8904,7 @@
         <v>1628</v>
       </c>
       <c r="W16" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8963,7 +8966,7 @@
         <v>1629</v>
       </c>
       <c r="W17" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -9025,7 +9028,7 @@
         <v>1620</v>
       </c>
       <c r="W18" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -9087,7 +9090,7 @@
         <v>1620</v>
       </c>
       <c r="W19" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -9149,7 +9152,7 @@
         <v>1630</v>
       </c>
       <c r="W20" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -9211,7 +9214,7 @@
         <v>1631</v>
       </c>
       <c r="W21" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -9273,7 +9276,7 @@
         <v>1631</v>
       </c>
       <c r="W22" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -9335,7 +9338,7 @@
         <v>1632</v>
       </c>
       <c r="W23" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -9394,7 +9397,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -9453,7 +9456,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9515,7 +9518,7 @@
         <v>1620</v>
       </c>
       <c r="W26" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9574,7 +9577,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9633,7 +9636,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9695,7 +9698,7 @@
         <v>1633</v>
       </c>
       <c r="W29" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9754,7 +9757,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9816,7 +9819,7 @@
         <v>1634</v>
       </c>
       <c r="W31" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9878,7 +9881,7 @@
         <v>1635</v>
       </c>
       <c r="W32" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9940,7 +9943,7 @@
         <v>1636</v>
       </c>
       <c r="W33" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -10002,7 +10005,7 @@
         <v>1637</v>
       </c>
       <c r="W34" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -10064,7 +10067,7 @@
         <v>1638</v>
       </c>
       <c r="W35" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -10126,7 +10129,7 @@
         <v>1634</v>
       </c>
       <c r="W36" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -10188,7 +10191,7 @@
         <v>1639</v>
       </c>
       <c r="W37" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -10250,7 +10253,7 @@
         <v>1617</v>
       </c>
       <c r="W38" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -10312,7 +10315,7 @@
         <v>1636</v>
       </c>
       <c r="W39" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -10374,7 +10377,7 @@
         <v>1640</v>
       </c>
       <c r="W40" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -10436,7 +10439,7 @@
         <v>1641</v>
       </c>
       <c r="W41" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10498,16 +10501,16 @@
         <v>1642</v>
       </c>
       <c r="W42" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X42" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="Y42" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z42" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10569,7 +10572,7 @@
         <v>1636</v>
       </c>
       <c r="W43" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10631,7 +10634,7 @@
         <v>1643</v>
       </c>
       <c r="W44" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10693,7 +10696,7 @@
         <v>1636</v>
       </c>
       <c r="W45" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10755,7 +10758,7 @@
         <v>1636</v>
       </c>
       <c r="W46" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10817,7 +10820,7 @@
         <v>1644</v>
       </c>
       <c r="W47" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10879,7 +10882,7 @@
         <v>1645</v>
       </c>
       <c r="W48" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10941,7 +10944,7 @@
         <v>1646</v>
       </c>
       <c r="W49" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -11003,7 +11006,7 @@
         <v>1647</v>
       </c>
       <c r="W50" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -11065,7 +11068,7 @@
         <v>1648</v>
       </c>
       <c r="W51" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -11127,7 +11130,7 @@
         <v>1637</v>
       </c>
       <c r="W52" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -11189,7 +11192,7 @@
         <v>1631</v>
       </c>
       <c r="W53" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -11251,7 +11254,7 @@
         <v>1631</v>
       </c>
       <c r="W54" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -11313,7 +11316,7 @@
         <v>1631</v>
       </c>
       <c r="W55" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -11375,7 +11378,7 @@
         <v>1649</v>
       </c>
       <c r="W56" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -11437,7 +11440,7 @@
         <v>1650</v>
       </c>
       <c r="W57" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11499,16 +11502,16 @@
         <v>1651</v>
       </c>
       <c r="W58" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X58" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="Y58" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z58" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11570,7 +11573,7 @@
         <v>1652</v>
       </c>
       <c r="W59" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11632,7 +11635,7 @@
         <v>1653</v>
       </c>
       <c r="W60" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11694,7 +11697,7 @@
         <v>1631</v>
       </c>
       <c r="W61" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11756,7 +11759,7 @@
         <v>1654</v>
       </c>
       <c r="W62" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11815,7 +11818,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11874,7 +11877,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11933,7 +11936,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11992,7 +11995,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -12051,7 +12054,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -12110,7 +12113,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -12172,7 +12175,7 @@
         <v>1655</v>
       </c>
       <c r="W69" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -12234,7 +12237,7 @@
         <v>1653</v>
       </c>
       <c r="W70" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -12296,7 +12299,7 @@
         <v>1638</v>
       </c>
       <c r="W71" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -12358,7 +12361,7 @@
         <v>1656</v>
       </c>
       <c r="W72" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -12420,7 +12423,7 @@
         <v>1657</v>
       </c>
       <c r="W73" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12482,16 +12485,16 @@
         <v>1658</v>
       </c>
       <c r="W74" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X74" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="Y74" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z74" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12553,16 +12556,16 @@
         <v>1659</v>
       </c>
       <c r="W75" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X75" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="Y75" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z75" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12624,7 +12627,7 @@
         <v>1638</v>
       </c>
       <c r="W76" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12686,7 +12689,7 @@
         <v>1638</v>
       </c>
       <c r="W77" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12748,10 +12751,10 @@
         <v>1660</v>
       </c>
       <c r="W78" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="Z78" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12816,7 +12819,7 @@
         <v>1661</v>
       </c>
       <c r="W79" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12875,7 +12878,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12934,7 +12937,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12996,7 +12999,7 @@
         <v>1662</v>
       </c>
       <c r="W82" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -13058,7 +13061,7 @@
         <v>1663</v>
       </c>
       <c r="W83" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -13120,7 +13123,7 @@
         <v>1664</v>
       </c>
       <c r="W84" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -13179,7 +13182,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -13241,7 +13244,7 @@
         <v>1665</v>
       </c>
       <c r="W86" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -13303,7 +13306,7 @@
         <v>1666</v>
       </c>
       <c r="W87" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -13365,7 +13368,7 @@
         <v>1666</v>
       </c>
       <c r="W88" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -13427,7 +13430,7 @@
         <v>1631</v>
       </c>
       <c r="W89" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13489,16 +13492,16 @@
         <v>1667</v>
       </c>
       <c r="W90" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X90" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Y90" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z90" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13560,16 +13563,16 @@
         <v>1668</v>
       </c>
       <c r="W91" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X91" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="Y91" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z91" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13631,7 +13634,7 @@
         <v>1669</v>
       </c>
       <c r="W92" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13693,7 +13696,7 @@
         <v>1670</v>
       </c>
       <c r="W93" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13755,7 +13758,7 @@
         <v>1670</v>
       </c>
       <c r="W94" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13817,7 +13820,7 @@
         <v>1671</v>
       </c>
       <c r="W95" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13879,16 +13882,16 @@
         <v>1672</v>
       </c>
       <c r="W96" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X96" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Y96" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z96" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13950,7 +13953,7 @@
         <v>1673</v>
       </c>
       <c r="W97" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -14012,7 +14015,7 @@
         <v>1674</v>
       </c>
       <c r="W98" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -14074,7 +14077,7 @@
         <v>1675</v>
       </c>
       <c r="W99" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -14136,7 +14139,7 @@
         <v>1676</v>
       </c>
       <c r="W100" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -14198,16 +14201,16 @@
         <v>1677</v>
       </c>
       <c r="W101" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X101" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="Y101" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z101" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -14269,7 +14272,7 @@
         <v>1678</v>
       </c>
       <c r="W102" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -14331,7 +14334,7 @@
         <v>1678</v>
       </c>
       <c r="W103" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -14393,7 +14396,7 @@
         <v>1679</v>
       </c>
       <c r="W104" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -14455,16 +14458,16 @@
         <v>1680</v>
       </c>
       <c r="W105" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X105" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="Y105" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z105" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14526,16 +14529,16 @@
         <v>1681</v>
       </c>
       <c r="W106" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X106" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="Y106" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z106" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14597,7 +14600,7 @@
         <v>1682</v>
       </c>
       <c r="W107" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14659,16 +14662,16 @@
         <v>1683</v>
       </c>
       <c r="W108" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X108" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="Y108" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z108" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14730,16 +14733,16 @@
         <v>1684</v>
       </c>
       <c r="W109" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X109" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="Y109" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z109" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14798,7 +14801,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14860,16 +14863,16 @@
         <v>1685</v>
       </c>
       <c r="W111" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X111" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="Y111" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z111" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14931,16 +14934,16 @@
         <v>1686</v>
       </c>
       <c r="W112" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X112" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="Y112" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z112" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -15002,16 +15005,16 @@
         <v>1687</v>
       </c>
       <c r="W113" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X113" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="Y113" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z113" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -15073,16 +15076,16 @@
         <v>1688</v>
       </c>
       <c r="W114" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X114" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="Y114" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z114" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -15144,16 +15147,16 @@
         <v>1684</v>
       </c>
       <c r="W115" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X115" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="Y115" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z115" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -15215,16 +15218,16 @@
         <v>1684</v>
       </c>
       <c r="W116" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X116" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="Y116" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z116" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -15286,16 +15289,16 @@
         <v>1689</v>
       </c>
       <c r="W117" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X117" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="Y117" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z117" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -15357,16 +15360,16 @@
         <v>1690</v>
       </c>
       <c r="W118" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X118" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="Y118" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z118" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -15428,7 +15431,7 @@
         <v>1691</v>
       </c>
       <c r="W119" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15490,16 +15493,16 @@
         <v>1692</v>
       </c>
       <c r="W120" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X120" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y120" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z120" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15561,16 +15564,16 @@
         <v>1692</v>
       </c>
       <c r="W121" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X121" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y121" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z121" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15632,16 +15635,16 @@
         <v>1692</v>
       </c>
       <c r="W122" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X122" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y122" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z122" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15703,16 +15706,16 @@
         <v>1692</v>
       </c>
       <c r="W123" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X123" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y123" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z123" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15774,16 +15777,16 @@
         <v>1692</v>
       </c>
       <c r="W124" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X124" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y124" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z124" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15845,16 +15848,16 @@
         <v>1692</v>
       </c>
       <c r="W125" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X125" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y125" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z125" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15916,16 +15919,16 @@
         <v>1692</v>
       </c>
       <c r="W126" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X126" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y126" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z126" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15987,16 +15990,16 @@
         <v>1693</v>
       </c>
       <c r="W127" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X127" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="Y127" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z127" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -16058,16 +16061,16 @@
         <v>1694</v>
       </c>
       <c r="W128" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X128" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="Y128" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z128" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -16129,16 +16132,16 @@
         <v>1692</v>
       </c>
       <c r="W129" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X129" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y129" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z129" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -16200,16 +16203,16 @@
         <v>1692</v>
       </c>
       <c r="W130" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X130" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y130" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z130" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -16271,7 +16274,7 @@
         <v>1695</v>
       </c>
       <c r="W131" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -16330,7 +16333,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -16389,7 +16392,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -16451,16 +16454,16 @@
         <v>1692</v>
       </c>
       <c r="W134" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X134" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y134" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z134" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16522,16 +16525,16 @@
         <v>1692</v>
       </c>
       <c r="W135" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X135" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y135" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z135" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16593,7 +16596,7 @@
         <v>1691</v>
       </c>
       <c r="W136" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16652,7 +16655,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16714,16 +16717,16 @@
         <v>1696</v>
       </c>
       <c r="W138" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X138" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="Y138" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z138" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16785,16 +16788,16 @@
         <v>1684</v>
       </c>
       <c r="W139" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X139" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="Y139" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z139" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16856,16 +16859,16 @@
         <v>1692</v>
       </c>
       <c r="W140" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X140" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y140" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z140" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16924,7 +16927,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16983,7 +16986,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -17045,16 +17048,16 @@
         <v>1697</v>
       </c>
       <c r="W143" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X143" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="Y143" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z143" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -17116,16 +17119,16 @@
         <v>1698</v>
       </c>
       <c r="W144" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X144" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="Y144" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z144" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -17187,16 +17190,16 @@
         <v>1699</v>
       </c>
       <c r="W145" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X145" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="Y145" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z145" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -17258,16 +17261,16 @@
         <v>1700</v>
       </c>
       <c r="W146" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X146" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="Y146" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z146" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -17326,7 +17329,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -17388,7 +17391,7 @@
         <v>1701</v>
       </c>
       <c r="W148" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -17450,16 +17453,16 @@
         <v>1702</v>
       </c>
       <c r="W149" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X149" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="Y149" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z149" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17521,7 +17524,7 @@
         <v>1703</v>
       </c>
       <c r="W150" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17583,16 +17586,16 @@
         <v>1704</v>
       </c>
       <c r="W151" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X151" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="Y151" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z151" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17654,7 +17657,7 @@
         <v>1703</v>
       </c>
       <c r="W152" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17716,7 +17719,7 @@
         <v>1701</v>
       </c>
       <c r="W153" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17778,7 +17781,7 @@
         <v>1703</v>
       </c>
       <c r="W154" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17834,7 +17837,7 @@
         <v>-45853</v>
       </c>
       <c r="W155" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17896,7 +17899,7 @@
         <v>1703</v>
       </c>
       <c r="W156" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17958,16 +17961,16 @@
         <v>1705</v>
       </c>
       <c r="W157" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X157" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Y157" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z157" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -18029,7 +18032,7 @@
         <v>1701</v>
       </c>
       <c r="W158" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -18091,16 +18094,16 @@
         <v>1706</v>
       </c>
       <c r="W159" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X159" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Y159" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z159" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -18162,16 +18165,16 @@
         <v>1707</v>
       </c>
       <c r="W160" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X160" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="Y160" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z160" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -18233,16 +18236,16 @@
         <v>1706</v>
       </c>
       <c r="W161" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X161" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Y161" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z161" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -18304,16 +18307,16 @@
         <v>1706</v>
       </c>
       <c r="W162" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X162" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Y162" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z162" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -18375,16 +18378,16 @@
         <v>1706</v>
       </c>
       <c r="W163" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X163" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Y163" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z163" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18446,16 +18449,16 @@
         <v>1708</v>
       </c>
       <c r="W164" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X164" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="Y164" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z164" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18517,16 +18520,16 @@
         <v>1709</v>
       </c>
       <c r="W165" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X165" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="Y165" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z165" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18588,16 +18591,16 @@
         <v>1710</v>
       </c>
       <c r="W166" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X166" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="Y166" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z166" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18659,16 +18662,16 @@
         <v>1711</v>
       </c>
       <c r="W167" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X167" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="Y167" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z167" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18730,16 +18733,16 @@
         <v>1689</v>
       </c>
       <c r="W168" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X168" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="Y168" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z168" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18801,16 +18804,16 @@
         <v>1692</v>
       </c>
       <c r="W169" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X169" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y169" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z169" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18872,7 +18875,7 @@
         <v>1712</v>
       </c>
       <c r="W170" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18934,16 +18937,16 @@
         <v>1692</v>
       </c>
       <c r="W171" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X171" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y171" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z171" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -19005,16 +19008,16 @@
         <v>1713</v>
       </c>
       <c r="W172" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X172" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Y172" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z172" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -19076,16 +19079,16 @@
         <v>1714</v>
       </c>
       <c r="W173" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X173" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="Y173" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z173" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -19147,16 +19150,16 @@
         <v>1715</v>
       </c>
       <c r="W174" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X174" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="Y174" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z174" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -19218,16 +19221,16 @@
         <v>1716</v>
       </c>
       <c r="W175" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X175" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="Y175" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z175" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -19289,16 +19292,16 @@
         <v>1717</v>
       </c>
       <c r="W176" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X176" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="Y176" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z176" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -19360,16 +19363,16 @@
         <v>1718</v>
       </c>
       <c r="W177" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X177" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="Y177" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z177" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -19431,7 +19434,7 @@
         <v>1712</v>
       </c>
       <c r="W178" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19493,16 +19496,16 @@
         <v>1719</v>
       </c>
       <c r="W179" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X179" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="Y179" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z179" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19564,16 +19567,16 @@
         <v>1720</v>
       </c>
       <c r="W180" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X180" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Y180" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z180" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19635,7 +19638,7 @@
         <v>1721</v>
       </c>
       <c r="W181" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19697,16 +19700,16 @@
         <v>1722</v>
       </c>
       <c r="W182" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X182" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="Y182" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z182" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19768,16 +19771,16 @@
         <v>1722</v>
       </c>
       <c r="W183" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X183" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="Y183" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z183" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19839,16 +19842,16 @@
         <v>1723</v>
       </c>
       <c r="W184" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X184" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="Y184" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z184" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19910,16 +19913,16 @@
         <v>1724</v>
       </c>
       <c r="W185" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X185" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="Y185" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z185" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19981,16 +19984,16 @@
         <v>1725</v>
       </c>
       <c r="W186" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X186" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="Y186" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z186" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -20052,7 +20055,7 @@
         <v>1726</v>
       </c>
       <c r="W187" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -20114,7 +20117,7 @@
         <v>1727</v>
       </c>
       <c r="W188" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -20176,7 +20179,7 @@
         <v>1728</v>
       </c>
       <c r="W189" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -20238,7 +20241,7 @@
         <v>1729</v>
       </c>
       <c r="W190" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -20300,16 +20303,16 @@
         <v>1730</v>
       </c>
       <c r="W191" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X191" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="Y191" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z191" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -20371,16 +20374,16 @@
         <v>1731</v>
       </c>
       <c r="W192" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X192" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="Y192" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z192" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -20442,7 +20445,7 @@
         <v>1732</v>
       </c>
       <c r="W193" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20504,7 +20507,7 @@
         <v>1732</v>
       </c>
       <c r="W194" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20566,16 +20569,16 @@
         <v>1733</v>
       </c>
       <c r="W195" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X195" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="Y195" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z195" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20637,16 +20640,16 @@
         <v>1734</v>
       </c>
       <c r="W196" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X196" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="Y196" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z196" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20708,16 +20711,16 @@
         <v>1735</v>
       </c>
       <c r="W197" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X197" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="Y197" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z197" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20779,16 +20782,16 @@
         <v>1731</v>
       </c>
       <c r="W198" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X198" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="Y198" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z198" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20850,7 +20853,7 @@
         <v>1736</v>
       </c>
       <c r="W199" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20912,7 +20915,7 @@
         <v>1737</v>
       </c>
       <c r="W200" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20974,16 +20977,16 @@
         <v>1738</v>
       </c>
       <c r="W201" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X201" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="Y201" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z201" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -21045,16 +21048,16 @@
         <v>1738</v>
       </c>
       <c r="W202" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X202" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="Y202" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z202" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -21116,16 +21119,16 @@
         <v>1739</v>
       </c>
       <c r="W203" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X203" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="Y203" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z203" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -21187,16 +21190,16 @@
         <v>1740</v>
       </c>
       <c r="W204" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X204" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="Y204" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z204" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -21258,16 +21261,16 @@
         <v>1741</v>
       </c>
       <c r="W205" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X205" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="Y205" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z205" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -21329,16 +21332,16 @@
         <v>1742</v>
       </c>
       <c r="W206" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X206" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="Y206" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z206" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -21400,16 +21403,16 @@
         <v>1743</v>
       </c>
       <c r="W207" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X207" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="Y207" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z207" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21471,16 +21474,16 @@
         <v>1744</v>
       </c>
       <c r="W208" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X208" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="Y208" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z208" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21542,16 +21545,16 @@
         <v>1745</v>
       </c>
       <c r="W209" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X209" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="Y209" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z209" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21613,7 +21616,7 @@
         <v>1746</v>
       </c>
       <c r="W210" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21675,16 +21678,16 @@
         <v>1747</v>
       </c>
       <c r="W211" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X211" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="Y211" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z211" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21746,16 +21749,16 @@
         <v>1748</v>
       </c>
       <c r="W212" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X212" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="Y212" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z212" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21817,16 +21820,16 @@
         <v>1749</v>
       </c>
       <c r="W213" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X213" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="Y213" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z213" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21888,16 +21891,16 @@
         <v>1750</v>
       </c>
       <c r="W214" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X214" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="Y214" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z214" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21959,7 +21962,7 @@
         <v>1751</v>
       </c>
       <c r="W215" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -22021,16 +22024,16 @@
         <v>1716</v>
       </c>
       <c r="W216" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X216" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="Y216" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z216" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -22092,16 +22095,16 @@
         <v>1752</v>
       </c>
       <c r="W217" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X217" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="Y217" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z217" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -22163,7 +22166,7 @@
         <v>1753</v>
       </c>
       <c r="W218" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -22225,16 +22228,16 @@
         <v>1754</v>
       </c>
       <c r="W219" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X219" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="Y219" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z219" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -22296,16 +22299,16 @@
         <v>1755</v>
       </c>
       <c r="W220" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X220" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="Y220" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z220" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -22367,7 +22370,7 @@
         <v>1756</v>
       </c>
       <c r="W221" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -22429,7 +22432,7 @@
         <v>1757</v>
       </c>
       <c r="W222" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22491,7 +22494,7 @@
         <v>1756</v>
       </c>
       <c r="W223" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22553,7 +22556,7 @@
         <v>1757</v>
       </c>
       <c r="W224" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22615,16 +22618,16 @@
         <v>1758</v>
       </c>
       <c r="W225" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X225" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="Y225" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z225" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22686,16 +22689,16 @@
         <v>1759</v>
       </c>
       <c r="W226" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X226" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="Y226" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z226" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22757,7 +22760,7 @@
         <v>1760</v>
       </c>
       <c r="W227" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22819,7 +22822,7 @@
         <v>1761</v>
       </c>
       <c r="W228" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22881,7 +22884,7 @@
         <v>1762</v>
       </c>
       <c r="W229" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22943,16 +22946,16 @@
         <v>1763</v>
       </c>
       <c r="W230" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X230" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="Y230" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z230" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -23014,16 +23017,16 @@
         <v>1764</v>
       </c>
       <c r="W231" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X231" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="Y231" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z231" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -23085,16 +23088,16 @@
         <v>1765</v>
       </c>
       <c r="W232" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X232" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="Y232" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z232" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -23159,16 +23162,16 @@
         <v>1766</v>
       </c>
       <c r="W233" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X233" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="Y233" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z233" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -23230,16 +23233,16 @@
         <v>1767</v>
       </c>
       <c r="W234" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X234" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="Y234" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z234" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -23301,16 +23304,16 @@
         <v>1768</v>
       </c>
       <c r="W235" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X235" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="Y235" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z235" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -23372,16 +23375,16 @@
         <v>1768</v>
       </c>
       <c r="W236" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X236" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="Y236" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z236" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -23443,16 +23446,16 @@
         <v>1769</v>
       </c>
       <c r="W237" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X237" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="Y237" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z237" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23514,7 +23517,7 @@
         <v>1770</v>
       </c>
       <c r="W238" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23576,7 +23579,7 @@
         <v>1771</v>
       </c>
       <c r="W239" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23638,16 +23641,16 @@
         <v>1772</v>
       </c>
       <c r="W240" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X240" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="Y240" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z240" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23709,16 +23712,16 @@
         <v>1773</v>
       </c>
       <c r="W241" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X241" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="Y241" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z241" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23780,7 +23783,7 @@
         <v>1774</v>
       </c>
       <c r="W242" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23842,16 +23845,16 @@
         <v>1775</v>
       </c>
       <c r="W243" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X243" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="Y243" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z243" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23913,16 +23916,16 @@
         <v>1776</v>
       </c>
       <c r="W244" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X244" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="Y244" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z244" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23984,16 +23987,16 @@
         <v>1775</v>
       </c>
       <c r="W245" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X245" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="Y245" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z245" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -24055,16 +24058,16 @@
         <v>1777</v>
       </c>
       <c r="W246" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X246" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="Y246" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z246" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -24126,16 +24129,16 @@
         <v>1776</v>
       </c>
       <c r="W247" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X247" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="Y247" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z247" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -24197,16 +24200,16 @@
         <v>1777</v>
       </c>
       <c r="W248" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X248" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="Y248" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z248" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -24268,16 +24271,16 @@
         <v>1778</v>
       </c>
       <c r="W249" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X249" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="Y249" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z249" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -24339,16 +24342,16 @@
         <v>1768</v>
       </c>
       <c r="W250" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X250" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="Y250" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z250" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -24410,7 +24413,7 @@
         <v>1779</v>
       </c>
       <c r="W251" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24472,7 +24475,7 @@
         <v>1780</v>
       </c>
       <c r="W252" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24534,16 +24537,16 @@
         <v>1781</v>
       </c>
       <c r="W253" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X253" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="Y253" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z253" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24605,16 +24608,16 @@
         <v>1782</v>
       </c>
       <c r="W254" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X254" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="Y254" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z254" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24676,7 +24679,7 @@
         <v>1783</v>
       </c>
       <c r="W255" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24738,16 +24741,16 @@
         <v>1784</v>
       </c>
       <c r="W256" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X256" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="Y256" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z256" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24809,7 +24812,7 @@
         <v>1785</v>
       </c>
       <c r="W257" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24874,7 +24877,7 @@
         <v>1786</v>
       </c>
       <c r="W258" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24936,7 +24939,7 @@
         <v>1787</v>
       </c>
       <c r="W259" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24998,7 +25001,7 @@
         <v>1787</v>
       </c>
       <c r="W260" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -25060,7 +25063,7 @@
         <v>1788</v>
       </c>
       <c r="W261" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -25122,16 +25125,16 @@
         <v>1789</v>
       </c>
       <c r="W262" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X262" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="Y262" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z262" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -25193,13 +25196,13 @@
         <v>1790</v>
       </c>
       <c r="W263" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X263" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="Y263" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -25261,16 +25264,16 @@
         <v>1791</v>
       </c>
       <c r="W264" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X264" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="Y264" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z264" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -25332,7 +25335,7 @@
         <v>1792</v>
       </c>
       <c r="W265" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -25394,7 +25397,7 @@
         <v>1792</v>
       </c>
       <c r="W266" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25456,7 +25459,7 @@
         <v>1793</v>
       </c>
       <c r="W267" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25518,16 +25521,16 @@
         <v>1794</v>
       </c>
       <c r="W268" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X268" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="Y268" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z268" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25589,16 +25592,16 @@
         <v>1795</v>
       </c>
       <c r="W269" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X269" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="Y269" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z269" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25660,7 +25663,7 @@
         <v>1636</v>
       </c>
       <c r="W270" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25722,7 +25725,7 @@
         <v>1796</v>
       </c>
       <c r="W271" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25784,7 +25787,7 @@
         <v>1797</v>
       </c>
       <c r="W272" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25846,16 +25849,16 @@
         <v>1798</v>
       </c>
       <c r="W273" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X273" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="Y273" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z273" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25914,7 +25917,7 @@
         <v>7</v>
       </c>
       <c r="W274" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25976,7 +25979,7 @@
         <v>1799</v>
       </c>
       <c r="W275" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -26035,7 +26038,7 @@
         <v>7</v>
       </c>
       <c r="W276" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -26097,7 +26100,7 @@
         <v>1800</v>
       </c>
       <c r="W277" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -26159,7 +26162,7 @@
         <v>1801</v>
       </c>
       <c r="W278" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -26221,16 +26224,16 @@
         <v>1802</v>
       </c>
       <c r="W279" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X279" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="Y279" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z279" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -26292,16 +26295,16 @@
         <v>1803</v>
       </c>
       <c r="W280" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X280" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="Y280" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z280" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -26363,16 +26366,16 @@
         <v>1803</v>
       </c>
       <c r="W281" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X281" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="Y281" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z281" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -26434,16 +26437,16 @@
         <v>1804</v>
       </c>
       <c r="W282" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X282" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="Y282" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z282" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26505,7 +26508,7 @@
         <v>1805</v>
       </c>
       <c r="W283" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26567,7 +26570,7 @@
         <v>1806</v>
       </c>
       <c r="W284" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26629,7 +26632,7 @@
         <v>1807</v>
       </c>
       <c r="W285" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26691,16 +26694,16 @@
         <v>1808</v>
       </c>
       <c r="W286" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X286" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="Y286" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z286" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26762,7 +26765,7 @@
         <v>1809</v>
       </c>
       <c r="W287" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26824,16 +26827,16 @@
         <v>1803</v>
       </c>
       <c r="W288" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X288" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="Y288" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z288" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26895,16 +26898,16 @@
         <v>1810</v>
       </c>
       <c r="W289" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X289" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="Y289" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z289" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26966,7 +26969,7 @@
         <v>1811</v>
       </c>
       <c r="W290" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -27028,16 +27031,16 @@
         <v>1812</v>
       </c>
       <c r="W291" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X291" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="Y291" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z291" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -27099,16 +27102,16 @@
         <v>1813</v>
       </c>
       <c r="W292" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X292" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="Y292" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z292" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -27170,7 +27173,7 @@
         <v>1814</v>
       </c>
       <c r="W293" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -27229,7 +27232,7 @@
         <v>14</v>
       </c>
       <c r="W294" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -27291,7 +27294,7 @@
         <v>1815</v>
       </c>
       <c r="W295" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -27353,7 +27356,7 @@
         <v>1816</v>
       </c>
       <c r="W296" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -27415,7 +27418,7 @@
         <v>1817</v>
       </c>
       <c r="W297" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27477,13 +27480,13 @@
         <v>1818</v>
       </c>
       <c r="W298" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X298" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="Z298" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27545,7 +27548,7 @@
         <v>1819</v>
       </c>
       <c r="W299" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27607,7 +27610,7 @@
         <v>1820</v>
       </c>
       <c r="W300" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27669,7 +27672,7 @@
         <v>1821</v>
       </c>
       <c r="W301" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27731,7 +27734,7 @@
         <v>1822</v>
       </c>
       <c r="W302" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27793,7 +27796,7 @@
         <v>1823</v>
       </c>
       <c r="W303" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27855,16 +27858,16 @@
         <v>1824</v>
       </c>
       <c r="W304" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X304" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="Y304" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z304" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27926,7 +27929,7 @@
         <v>1825</v>
       </c>
       <c r="W305" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27988,7 +27991,7 @@
         <v>1826</v>
       </c>
       <c r="W306" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -28050,7 +28053,7 @@
         <v>1827</v>
       </c>
       <c r="W307" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -28112,7 +28115,7 @@
         <v>1828</v>
       </c>
       <c r="W308" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -28174,7 +28177,7 @@
         <v>1821</v>
       </c>
       <c r="W309" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -28236,7 +28239,7 @@
         <v>1829</v>
       </c>
       <c r="W310" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -28298,7 +28301,7 @@
         <v>1830</v>
       </c>
       <c r="W311" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -28360,7 +28363,7 @@
         <v>1831</v>
       </c>
       <c r="W312" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -28422,7 +28425,7 @@
         <v>1832</v>
       </c>
       <c r="W313" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28484,7 +28487,7 @@
         <v>1833</v>
       </c>
       <c r="W314" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28546,7 +28549,7 @@
         <v>1834</v>
       </c>
       <c r="W315" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28608,7 +28611,7 @@
         <v>1835</v>
       </c>
       <c r="W316" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28670,7 +28673,7 @@
         <v>1836</v>
       </c>
       <c r="W317" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28732,7 +28735,7 @@
         <v>1837</v>
       </c>
       <c r="W318" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28794,7 +28797,7 @@
         <v>1838</v>
       </c>
       <c r="W319" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28856,7 +28859,7 @@
         <v>1839</v>
       </c>
       <c r="W320" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28915,13 +28918,13 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X321" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="Z321" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28980,7 +28983,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -29039,7 +29042,7 @@
         <v>29</v>
       </c>
       <c r="W323" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -29098,7 +29101,7 @@
         <v>0</v>
       </c>
       <c r="W324" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -29160,7 +29163,7 @@
         <v>1840</v>
       </c>
       <c r="W325" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -29222,7 +29225,7 @@
         <v>1841</v>
       </c>
       <c r="W326" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -29284,7 +29287,7 @@
         <v>1842</v>
       </c>
       <c r="W327" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -29346,7 +29349,7 @@
         <v>1843</v>
       </c>
       <c r="W328" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -29405,7 +29408,7 @@
         <v>14</v>
       </c>
       <c r="W329" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29467,7 +29470,7 @@
         <v>1843</v>
       </c>
       <c r="W330" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29529,7 +29532,7 @@
         <v>1844</v>
       </c>
       <c r="W331" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29591,7 +29594,7 @@
         <v>1845</v>
       </c>
       <c r="W332" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29653,7 +29656,7 @@
         <v>1845</v>
       </c>
       <c r="W333" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29715,7 +29718,7 @@
         <v>1846</v>
       </c>
       <c r="W334" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29777,7 +29780,7 @@
         <v>1847</v>
       </c>
       <c r="W335" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29839,7 +29842,7 @@
         <v>1848</v>
       </c>
       <c r="W336" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29898,13 +29901,13 @@
         <v>12</v>
       </c>
       <c r="W337" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X337" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="Z337" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29966,7 +29969,7 @@
         <v>1849</v>
       </c>
       <c r="W338" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -30028,13 +30031,13 @@
         <v>1850</v>
       </c>
       <c r="W339" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X339" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="Z339" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -30096,13 +30099,13 @@
         <v>1851</v>
       </c>
       <c r="W340" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X340" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="Z340" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -30164,7 +30167,7 @@
         <v>1852</v>
       </c>
       <c r="W341" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -30226,7 +30229,7 @@
         <v>1853</v>
       </c>
       <c r="W342" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -30288,10 +30291,10 @@
         <v>1854</v>
       </c>
       <c r="W343" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X343" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -30353,7 +30356,7 @@
         <v>1855</v>
       </c>
       <c r="W344" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -30415,7 +30418,7 @@
         <v>1856</v>
       </c>
       <c r="W345" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30477,13 +30480,13 @@
         <v>1857</v>
       </c>
       <c r="W346" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X346" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="Z346" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30545,7 +30548,7 @@
         <v>1821</v>
       </c>
       <c r="W347" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30607,7 +30610,7 @@
         <v>1858</v>
       </c>
       <c r="W348" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30669,16 +30672,16 @@
         <v>1859</v>
       </c>
       <c r="W349" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X349" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="Y349" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z349" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30743,13 +30746,13 @@
         <v>1860</v>
       </c>
       <c r="W350" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X350" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="Z350" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30811,7 +30814,7 @@
         <v>1861</v>
       </c>
       <c r="W351" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30873,16 +30876,16 @@
         <v>1862</v>
       </c>
       <c r="W352" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X352" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="Y352" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z352" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30944,13 +30947,13 @@
         <v>1863</v>
       </c>
       <c r="W353" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X353" t="s">
         <v>1863</v>
       </c>
       <c r="Z353" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -31012,16 +31015,16 @@
         <v>1864</v>
       </c>
       <c r="W354" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X354" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="Y354" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z354" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -31083,7 +31086,7 @@
         <v>1865</v>
       </c>
       <c r="W355" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -31145,7 +31148,7 @@
         <v>1866</v>
       </c>
       <c r="W356" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -31204,7 +31207,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -31263,7 +31266,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -31322,7 +31325,7 @@
         <v>0</v>
       </c>
       <c r="W359" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -31384,7 +31387,7 @@
         <v>1867</v>
       </c>
       <c r="W360" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -31449,7 +31452,7 @@
         <v>1868</v>
       </c>
       <c r="W361" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31514,7 +31517,7 @@
         <v>1869</v>
       </c>
       <c r="W362" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31576,16 +31579,16 @@
         <v>1870</v>
       </c>
       <c r="W363" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X363" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="Y363" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z363" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31647,16 +31650,16 @@
         <v>1871</v>
       </c>
       <c r="W364" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X364" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="Y364" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z364" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31718,7 +31721,7 @@
         <v>1872</v>
       </c>
       <c r="W365" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31780,7 +31783,7 @@
         <v>1873</v>
       </c>
       <c r="W366" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31845,7 +31848,7 @@
         <v>1874</v>
       </c>
       <c r="W367" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31907,7 +31910,7 @@
         <v>1875</v>
       </c>
       <c r="W368" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31969,7 +31972,7 @@
         <v>1876</v>
       </c>
       <c r="W369" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -32034,13 +32037,13 @@
         <v>1877</v>
       </c>
       <c r="W370" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X370" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="Z370" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -32102,7 +32105,7 @@
         <v>1878</v>
       </c>
       <c r="W371" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -32164,16 +32167,16 @@
         <v>1879</v>
       </c>
       <c r="W372" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X372" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="Y372" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z372" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -32238,7 +32241,7 @@
         <v>1880</v>
       </c>
       <c r="W373" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -32303,16 +32306,16 @@
         <v>1881</v>
       </c>
       <c r="W374" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X374" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="Y374" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z374" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -32374,7 +32377,7 @@
         <v>1882</v>
       </c>
       <c r="W375" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -32439,7 +32442,7 @@
         <v>1883</v>
       </c>
       <c r="W376" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32504,7 +32507,7 @@
         <v>1884</v>
       </c>
       <c r="W377" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32569,7 +32572,7 @@
         <v>1884</v>
       </c>
       <c r="W378" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32634,13 +32637,13 @@
         <v>1885</v>
       </c>
       <c r="W379" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X379" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="Z379" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32702,16 +32705,16 @@
         <v>1886</v>
       </c>
       <c r="W380" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X380" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="Y380" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z380" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32776,7 +32779,7 @@
         <v>1887</v>
       </c>
       <c r="W381" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32838,7 +32841,7 @@
         <v>1888</v>
       </c>
       <c r="W382" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32903,7 +32906,7 @@
         <v>1889</v>
       </c>
       <c r="W383" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32965,7 +32968,7 @@
         <v>1890</v>
       </c>
       <c r="W384" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -33030,7 +33033,7 @@
         <v>1889</v>
       </c>
       <c r="W385" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -33092,16 +33095,16 @@
         <v>1891</v>
       </c>
       <c r="W386" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X386" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="Y386" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z386" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -33169,7 +33172,7 @@
         <v>1892</v>
       </c>
       <c r="W387" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -33231,7 +33234,7 @@
         <v>1893</v>
       </c>
       <c r="W388" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -33293,7 +33296,7 @@
         <v>1894</v>
       </c>
       <c r="W389" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -33355,16 +33358,16 @@
         <v>1895</v>
       </c>
       <c r="W390" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X390" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="Y390" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z390" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -33429,16 +33432,16 @@
         <v>1896</v>
       </c>
       <c r="W391" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X391" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="Y391" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z391" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33503,7 +33506,7 @@
         <v>1897</v>
       </c>
       <c r="W392" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33565,7 +33568,7 @@
         <v>1898</v>
       </c>
       <c r="W393" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33627,16 +33630,16 @@
         <v>1899</v>
       </c>
       <c r="W394" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X394" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="Y394" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z394" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33698,7 +33701,7 @@
         <v>1900</v>
       </c>
       <c r="W395" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33763,16 +33766,16 @@
         <v>1901</v>
       </c>
       <c r="W396" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X396" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="Y396" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z396" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33837,13 +33840,13 @@
         <v>1902</v>
       </c>
       <c r="W397" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X397" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="Y397" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33905,7 +33908,7 @@
         <v>1903</v>
       </c>
       <c r="W398" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33967,7 +33970,7 @@
         <v>1904</v>
       </c>
       <c r="W399" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -34032,7 +34035,7 @@
         <v>1905</v>
       </c>
       <c r="W400" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -34097,16 +34100,16 @@
         <v>1906</v>
       </c>
       <c r="W401" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X401" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="Y401" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z401" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -34171,7 +34174,7 @@
         <v>1907</v>
       </c>
       <c r="W402" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -34236,7 +34239,7 @@
         <v>1908</v>
       </c>
       <c r="W403" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -34301,16 +34304,16 @@
         <v>1909</v>
       </c>
       <c r="W404" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X404" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="Y404" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z404" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -34375,7 +34378,7 @@
         <v>1910</v>
       </c>
       <c r="W405" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -34440,7 +34443,7 @@
         <v>1911</v>
       </c>
       <c r="W406" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34508,7 +34511,7 @@
         <v>1912</v>
       </c>
       <c r="W407" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34570,16 +34573,16 @@
         <v>1913</v>
       </c>
       <c r="W408" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X408" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="Y408" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z408" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34644,13 +34647,13 @@
         <v>1914</v>
       </c>
       <c r="W409" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X409" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="Z409" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34715,7 +34718,7 @@
         <v>1915</v>
       </c>
       <c r="W410" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34780,7 +34783,7 @@
         <v>1916</v>
       </c>
       <c r="W411" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34845,7 +34848,7 @@
         <v>1917</v>
       </c>
       <c r="W412" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34910,7 +34913,7 @@
         <v>1918</v>
       </c>
       <c r="W413" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34975,7 +34978,7 @@
         <v>1919</v>
       </c>
       <c r="W414" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -35040,7 +35043,7 @@
         <v>1919</v>
       </c>
       <c r="W415" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -35105,7 +35108,7 @@
         <v>1920</v>
       </c>
       <c r="W416" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -35170,7 +35173,7 @@
         <v>1921</v>
       </c>
       <c r="W417" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -35235,7 +35238,7 @@
         <v>1919</v>
       </c>
       <c r="W418" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -35300,7 +35303,7 @@
         <v>1922</v>
       </c>
       <c r="W419" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -35365,7 +35368,7 @@
         <v>1923</v>
       </c>
       <c r="W420" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -35430,16 +35433,16 @@
         <v>1924</v>
       </c>
       <c r="W421" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X421" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="Y421" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z421" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35504,7 +35507,7 @@
         <v>1925</v>
       </c>
       <c r="W422" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35569,7 +35572,7 @@
         <v>1926</v>
       </c>
       <c r="W423" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35634,7 +35637,7 @@
         <v>1927</v>
       </c>
       <c r="W424" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35699,16 +35702,16 @@
         <v>1928</v>
       </c>
       <c r="W425" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X425" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="Y425" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z425" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35773,7 +35776,7 @@
         <v>1927</v>
       </c>
       <c r="W426" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35838,7 +35841,7 @@
         <v>1929</v>
       </c>
       <c r="W427" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35903,7 +35906,7 @@
         <v>1930</v>
       </c>
       <c r="W428" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35968,13 +35971,13 @@
         <v>1931</v>
       </c>
       <c r="W429" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X429" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="Y429" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -36039,16 +36042,16 @@
         <v>1932</v>
       </c>
       <c r="W430" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X430" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="Y430" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z430" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -36113,7 +36116,7 @@
         <v>1933</v>
       </c>
       <c r="W431" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -36178,16 +36181,16 @@
         <v>1934</v>
       </c>
       <c r="W432" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X432" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="Y432" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z432" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -36252,7 +36255,7 @@
         <v>1935</v>
       </c>
       <c r="W433" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -36317,7 +36320,7 @@
         <v>1936</v>
       </c>
       <c r="W434" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -36382,7 +36385,7 @@
         <v>1937</v>
       </c>
       <c r="W435" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -36447,7 +36450,7 @@
         <v>1938</v>
       </c>
       <c r="W436" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36512,7 +36515,7 @@
         <v>1939</v>
       </c>
       <c r="W437" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36577,7 +36580,7 @@
         <v>1940</v>
       </c>
       <c r="W438" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36642,7 +36645,7 @@
         <v>1941</v>
       </c>
       <c r="W439" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36707,7 +36710,7 @@
         <v>1942</v>
       </c>
       <c r="W440" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36772,16 +36775,16 @@
         <v>1943</v>
       </c>
       <c r="W441" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X441" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="Y441" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z441" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36846,16 +36849,16 @@
         <v>1944</v>
       </c>
       <c r="W442" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X442" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="Y442" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z442" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36920,16 +36923,16 @@
         <v>1945</v>
       </c>
       <c r="W443" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X443" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="Y443" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z443" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36994,7 +36997,7 @@
         <v>1946</v>
       </c>
       <c r="W444" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -37059,7 +37062,7 @@
         <v>1947</v>
       </c>
       <c r="W445" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -37124,16 +37127,16 @@
         <v>1944</v>
       </c>
       <c r="W446" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X446" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="Y446" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z446" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -37198,16 +37201,16 @@
         <v>1944</v>
       </c>
       <c r="W447" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X447" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="Y447" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z447" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -37272,16 +37275,16 @@
         <v>1948</v>
       </c>
       <c r="W448" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X448" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="Y448" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z448" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -37346,16 +37349,16 @@
         <v>1944</v>
       </c>
       <c r="W449" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X449" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="Y449" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z449" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -37420,16 +37423,16 @@
         <v>1944</v>
       </c>
       <c r="W450" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X450" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="Y450" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z450" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37494,16 +37497,16 @@
         <v>1949</v>
       </c>
       <c r="W451" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X451" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="Y451" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z451" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37568,16 +37571,16 @@
         <v>1950</v>
       </c>
       <c r="W452" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X452" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="Y452" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z452" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37642,7 +37645,7 @@
         <v>1951</v>
       </c>
       <c r="W453" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37707,16 +37710,16 @@
         <v>1952</v>
       </c>
       <c r="W454" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X454" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="Y454" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z454" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37781,16 +37784,16 @@
         <v>1953</v>
       </c>
       <c r="W455" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X455" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="Y455" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z455" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37855,16 +37858,16 @@
         <v>1954</v>
       </c>
       <c r="W456" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X456" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="Y456" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z456" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37929,16 +37932,16 @@
         <v>1955</v>
       </c>
       <c r="W457" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X457" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="Y457" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z457" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -38003,7 +38006,7 @@
         <v>1956</v>
       </c>
       <c r="W458" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -38068,7 +38071,7 @@
         <v>1956</v>
       </c>
       <c r="W459" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -38133,16 +38136,16 @@
         <v>1954</v>
       </c>
       <c r="W460" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X460" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="Y460" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z460" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -38207,16 +38210,16 @@
         <v>1957</v>
       </c>
       <c r="W461" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X461" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="Y461" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z461" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -38281,16 +38284,16 @@
         <v>1958</v>
       </c>
       <c r="W462" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X462" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="Y462" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z462" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -38355,7 +38358,7 @@
         <v>1959</v>
       </c>
       <c r="W463" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -38420,16 +38423,16 @@
         <v>1960</v>
       </c>
       <c r="W464" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X464" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="Y464" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z464" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38494,16 +38497,16 @@
         <v>1961</v>
       </c>
       <c r="W465" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X465" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="Y465" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z465" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38568,16 +38571,16 @@
         <v>1962</v>
       </c>
       <c r="W466" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X466" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="Y466" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z466" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38642,7 +38645,7 @@
         <v>1963</v>
       </c>
       <c r="W467" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38707,16 +38710,16 @@
         <v>1964</v>
       </c>
       <c r="W468" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X468" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="Y468" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z468" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38781,16 +38784,16 @@
         <v>1965</v>
       </c>
       <c r="W469" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X469" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="Y469" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z469" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38855,16 +38858,16 @@
         <v>1966</v>
       </c>
       <c r="W470" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X470" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="Y470" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z470" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38929,16 +38932,16 @@
         <v>1967</v>
       </c>
       <c r="W471" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X471" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="Y471" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z471" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -39003,7 +39006,7 @@
         <v>1968</v>
       </c>
       <c r="W472" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -39068,16 +39071,16 @@
         <v>1969</v>
       </c>
       <c r="W473" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X473" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="Y473" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z473" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -39142,16 +39145,16 @@
         <v>1969</v>
       </c>
       <c r="W474" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X474" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="Y474" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z474" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -39216,7 +39219,7 @@
         <v>1970</v>
       </c>
       <c r="W475" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -39281,16 +39284,16 @@
         <v>1971</v>
       </c>
       <c r="W476" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X476" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="Y476" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z476" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -39355,16 +39358,16 @@
         <v>1972</v>
       </c>
       <c r="W477" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X477" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="Y477" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z477" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -39429,7 +39432,7 @@
         <v>1973</v>
       </c>
       <c r="W478" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39494,7 +39497,7 @@
         <v>1974</v>
       </c>
       <c r="W479" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39559,16 +39562,16 @@
         <v>1975</v>
       </c>
       <c r="W480" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X480" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="Y480" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z480" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39633,16 +39636,16 @@
         <v>1976</v>
       </c>
       <c r="W481" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X481" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="Y481" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z481" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39707,16 +39710,16 @@
         <v>1977</v>
       </c>
       <c r="W482" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X482" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="Y482" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z482" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39781,7 +39784,7 @@
         <v>1978</v>
       </c>
       <c r="W483" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39846,7 +39849,7 @@
         <v>1979</v>
       </c>
       <c r="W484" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39914,13 +39917,13 @@
         <v>1980</v>
       </c>
       <c r="W485" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X485">
         <v>12738616480</v>
       </c>
       <c r="Z485" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39985,7 +39988,7 @@
         <v>1981</v>
       </c>
       <c r="W486" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -40053,13 +40056,13 @@
         <v>1982</v>
       </c>
       <c r="W487" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X487">
         <v>12738616480</v>
       </c>
       <c r="Z487" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -40124,7 +40127,7 @@
         <v>1983</v>
       </c>
       <c r="W488" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -40189,16 +40192,16 @@
         <v>1984</v>
       </c>
       <c r="W489" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X489" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="Y489" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z489" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -40263,7 +40266,7 @@
         <v>1985</v>
       </c>
       <c r="W490" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -40331,13 +40334,13 @@
         <v>1986</v>
       </c>
       <c r="W491" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X491">
         <v>12738926716</v>
       </c>
       <c r="Z491" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -40402,16 +40405,16 @@
         <v>1987</v>
       </c>
       <c r="W492" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X492" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="Y492" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z492" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40476,16 +40479,16 @@
         <v>1988</v>
       </c>
       <c r="W493" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X493" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="Y493" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z493" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40550,16 +40553,16 @@
         <v>1989</v>
       </c>
       <c r="W494" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X494" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="Y494" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z494" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40624,13 +40627,13 @@
         <v>1990</v>
       </c>
       <c r="W495" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X495" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="Y495" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40695,16 +40698,16 @@
         <v>1991</v>
       </c>
       <c r="W496" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X496" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="Y496" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z496" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40769,7 +40772,7 @@
         <v>1992</v>
       </c>
       <c r="W497" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40837,7 +40840,7 @@
         <v>1993</v>
       </c>
       <c r="W498" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40902,7 +40905,7 @@
         <v>1994</v>
       </c>
       <c r="W499" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40970,7 +40973,7 @@
         <v>1995</v>
       </c>
       <c r="W500" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -41035,16 +41038,16 @@
         <v>1996</v>
       </c>
       <c r="W501" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X501" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="Y501" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z501" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -41109,16 +41112,16 @@
         <v>1997</v>
       </c>
       <c r="W502" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X502" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="Y502" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z502" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -41183,7 +41186,7 @@
         <v>1998</v>
       </c>
       <c r="W503" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -41251,7 +41254,7 @@
         <v>1999</v>
       </c>
       <c r="W504" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -41319,16 +41322,16 @@
         <v>2000</v>
       </c>
       <c r="W505" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X505" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="Y505" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z505" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -41393,7 +41396,7 @@
         <v>2001</v>
       </c>
       <c r="W506" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41458,16 +41461,16 @@
         <v>2002</v>
       </c>
       <c r="W507" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X507" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="Y507" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z507" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41532,7 +41535,7 @@
         <v>2003</v>
       </c>
       <c r="W508" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41597,7 +41600,7 @@
         <v>2004</v>
       </c>
       <c r="W509" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41662,16 +41665,16 @@
         <v>2005</v>
       </c>
       <c r="W510" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X510" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="Y510" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z510" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41736,16 +41739,16 @@
         <v>2006</v>
       </c>
       <c r="W511" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X511" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="Y511" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z511" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41813,7 +41816,7 @@
         <v>2007</v>
       </c>
       <c r="W512" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41881,7 +41884,7 @@
         <v>2008</v>
       </c>
       <c r="W513" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41949,7 +41952,7 @@
         <v>2009</v>
       </c>
       <c r="W514" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -42017,7 +42020,7 @@
         <v>2009</v>
       </c>
       <c r="W515" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -42085,7 +42088,7 @@
         <v>2009</v>
       </c>
       <c r="W516" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -42153,13 +42156,13 @@
         <v>2010</v>
       </c>
       <c r="W517" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X517">
         <v>12743527212</v>
       </c>
       <c r="Z517" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -42227,13 +42230,13 @@
         <v>2011</v>
       </c>
       <c r="W518" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X518">
         <v>12743529135</v>
       </c>
       <c r="Z518" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -42301,16 +42304,16 @@
         <v>2012</v>
       </c>
       <c r="W519" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X519" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="Y519" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z519" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -42378,16 +42381,16 @@
         <v>2013</v>
       </c>
       <c r="W520" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X520" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="Y520" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z520" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42452,7 +42455,7 @@
         <v>1616</v>
       </c>
       <c r="W521" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42520,7 +42523,7 @@
         <v>2014</v>
       </c>
       <c r="W522" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42588,7 +42591,7 @@
         <v>2014</v>
       </c>
       <c r="W523" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42656,7 +42659,7 @@
         <v>2015</v>
       </c>
       <c r="W524" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42724,7 +42727,7 @@
         <v>2016</v>
       </c>
       <c r="W525" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42792,7 +42795,7 @@
         <v>2017</v>
       </c>
       <c r="W526" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42860,7 +42863,7 @@
         <v>2018</v>
       </c>
       <c r="W527" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42928,7 +42931,7 @@
         <v>2019</v>
       </c>
       <c r="W528" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42993,7 +42996,7 @@
         <v>2020</v>
       </c>
       <c r="W529" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -43061,7 +43064,7 @@
         <v>2021</v>
       </c>
       <c r="W530" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -43129,16 +43132,16 @@
         <v>2022</v>
       </c>
       <c r="W531" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X531" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="Y531" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z531" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -43206,7 +43209,7 @@
         <v>2023</v>
       </c>
       <c r="W532" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -43271,7 +43274,7 @@
         <v>2024</v>
       </c>
       <c r="W533" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -43339,16 +43342,16 @@
         <v>2025</v>
       </c>
       <c r="W534" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X534" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="Y534" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z534" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -43416,13 +43419,13 @@
         <v>2026</v>
       </c>
       <c r="W535" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X535">
         <v>12743527212</v>
       </c>
       <c r="Z535" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43490,7 +43493,7 @@
         <v>2027</v>
       </c>
       <c r="W536" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43558,7 +43561,7 @@
         <v>2028</v>
       </c>
       <c r="W537" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43626,16 +43629,16 @@
         <v>2029</v>
       </c>
       <c r="W538" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X538" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="Y538" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z538" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43703,7 +43706,7 @@
         <v>2030</v>
       </c>
       <c r="W539" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43771,7 +43774,7 @@
         <v>2031</v>
       </c>
       <c r="W540" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43839,7 +43842,7 @@
         <v>2032</v>
       </c>
       <c r="W541" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43907,7 +43910,7 @@
         <v>2033</v>
       </c>
       <c r="W542" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43975,16 +43978,16 @@
         <v>2034</v>
       </c>
       <c r="W543" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X543" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="Y543" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z543" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -44052,7 +44055,7 @@
         <v>2035</v>
       </c>
       <c r="W544" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -44120,16 +44123,16 @@
         <v>2036</v>
       </c>
       <c r="W545" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X545" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="Y545" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="Z545" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -44197,7 +44200,7 @@
         <v>2037</v>
       </c>
       <c r="W546" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -44265,7 +44268,7 @@
         <v>2038</v>
       </c>
       <c r="W547" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -44333,7 +44336,7 @@
         <v>2039</v>
       </c>
       <c r="W548" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -44401,7 +44404,7 @@
         <v>2040</v>
       </c>
       <c r="W549" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44469,7 +44472,7 @@
         <v>2040</v>
       </c>
       <c r="W550" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44537,7 +44540,7 @@
         <v>2041</v>
       </c>
       <c r="W551" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44602,7 +44605,7 @@
         <v>2042</v>
       </c>
       <c r="W552" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44670,7 +44673,7 @@
         <v>2043</v>
       </c>
       <c r="W553" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44735,7 +44738,7 @@
         <v>2044</v>
       </c>
       <c r="W554" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44803,7 +44806,7 @@
         <v>2045</v>
       </c>
       <c r="W555" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44871,7 +44874,7 @@
         <v>2046</v>
       </c>
       <c r="W556" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44939,7 +44942,7 @@
         <v>2047</v>
       </c>
       <c r="W557" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -45004,7 +45007,7 @@
         <v>2048</v>
       </c>
       <c r="W558" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -45072,7 +45075,7 @@
         <v>2049</v>
       </c>
       <c r="W559" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -45140,7 +45143,7 @@
         <v>2050</v>
       </c>
       <c r="W560" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -45205,7 +45208,7 @@
         <v>2051</v>
       </c>
       <c r="W561" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -45273,7 +45276,7 @@
         <v>2052</v>
       </c>
       <c r="W562" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA562" t="b">
         <v>0</v>
@@ -45341,7 +45344,7 @@
         <v>2053</v>
       </c>
       <c r="W563" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -45406,7 +45409,7 @@
         <v>2054</v>
       </c>
       <c r="W564" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45474,7 +45477,7 @@
         <v>2055</v>
       </c>
       <c r="W565" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45542,7 +45545,7 @@
         <v>2056</v>
       </c>
       <c r="W566" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45610,7 +45613,7 @@
         <v>2057</v>
       </c>
       <c r="W567" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45678,7 +45681,7 @@
         <v>2058</v>
       </c>
       <c r="W568" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA568" t="b">
         <v>0</v>
@@ -45746,7 +45749,7 @@
         <v>2059</v>
       </c>
       <c r="W569" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45814,7 +45817,7 @@
         <v>2060</v>
       </c>
       <c r="W570" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45879,7 +45882,7 @@
         <v>2061</v>
       </c>
       <c r="W571" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45944,7 +45947,7 @@
         <v>2062</v>
       </c>
       <c r="W572" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -46012,7 +46015,7 @@
         <v>2063</v>
       </c>
       <c r="W573" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -46080,7 +46083,7 @@
         <v>2064</v>
       </c>
       <c r="W574" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -46148,7 +46151,7 @@
         <v>2065</v>
       </c>
       <c r="W575" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -46216,7 +46219,7 @@
         <v>2066</v>
       </c>
       <c r="W576" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -46284,7 +46287,7 @@
         <v>2067</v>
       </c>
       <c r="W577" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -46352,7 +46355,7 @@
         <v>2067</v>
       </c>
       <c r="W578" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -46420,7 +46423,7 @@
         <v>2068</v>
       </c>
       <c r="W579" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46488,7 +46491,7 @@
         <v>2069</v>
       </c>
       <c r="W580" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46556,7 +46559,7 @@
         <v>2070</v>
       </c>
       <c r="W581" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46624,7 +46627,7 @@
         <v>2071</v>
       </c>
       <c r="W582" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA582" t="b">
         <v>0</v>
@@ -46692,7 +46695,7 @@
         <v>2072</v>
       </c>
       <c r="W583" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA583" t="b">
         <v>0</v>
@@ -46760,7 +46763,7 @@
         <v>2073</v>
       </c>
       <c r="W584" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46828,7 +46831,7 @@
         <v>2074</v>
       </c>
       <c r="W585" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46896,7 +46899,7 @@
         <v>2074</v>
       </c>
       <c r="W586" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA586" t="b">
         <v>0</v>
@@ -46964,7 +46967,7 @@
         <v>2075</v>
       </c>
       <c r="W587" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA587" t="b">
         <v>0</v>
@@ -47032,7 +47035,7 @@
         <v>2076</v>
       </c>
       <c r="W588" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA588" t="b">
         <v>0</v>
@@ -47100,7 +47103,7 @@
         <v>2077</v>
       </c>
       <c r="W589" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA589" t="b">
         <v>0</v>
@@ -47168,7 +47171,7 @@
         <v>2078</v>
       </c>
       <c r="W590" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -47236,7 +47239,7 @@
         <v>2079</v>
       </c>
       <c r="W591" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA591" t="b">
         <v>0</v>
@@ -47304,7 +47307,7 @@
         <v>2080</v>
       </c>
       <c r="W592" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA592" t="b">
         <v>0</v>
@@ -47372,7 +47375,7 @@
         <v>2081</v>
       </c>
       <c r="W593" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA593" t="b">
         <v>0</v>
@@ -47440,7 +47443,7 @@
         <v>2080</v>
       </c>
       <c r="W594" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA594" t="b">
         <v>0</v>
@@ -47508,7 +47511,7 @@
         <v>2082</v>
       </c>
       <c r="W595" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA595" t="b">
         <v>0</v>
@@ -47576,7 +47579,7 @@
         <v>2083</v>
       </c>
       <c r="W596" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA596" t="b">
         <v>0</v>
@@ -47644,7 +47647,7 @@
         <v>2084</v>
       </c>
       <c r="W597" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA597" t="b">
         <v>0</v>
@@ -47712,7 +47715,7 @@
         <v>2085</v>
       </c>
       <c r="W598" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>
@@ -47762,10 +47765,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R599">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S599" t="s">
         <v>1613</v>
@@ -47777,10 +47780,10 @@
         <v>2086</v>
       </c>
       <c r="V599" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="W599" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA599" t="b">
         <v>1</v>
@@ -47848,7 +47851,7 @@
         <v>2087</v>
       </c>
       <c r="W600" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA600" t="b">
         <v>0</v>
@@ -47916,13 +47919,13 @@
         <v>2088</v>
       </c>
       <c r="W601" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="X601">
         <v>12760434076</v>
       </c>
       <c r="Z601" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="AA601" t="b">
         <v>0</v>
@@ -47990,7 +47993,7 @@
         <v>2089</v>
       </c>
       <c r="W602" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA602" t="b">
         <v>0</v>
@@ -48058,7 +48061,7 @@
         <v>2090</v>
       </c>
       <c r="W603" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA603" t="b">
         <v>0</v>
@@ -48126,7 +48129,7 @@
         <v>2091</v>
       </c>
       <c r="W604" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA604" t="b">
         <v>0</v>
@@ -48194,7 +48197,7 @@
         <v>2092</v>
       </c>
       <c r="W605" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA605" t="b">
         <v>0</v>
@@ -48262,7 +48265,7 @@
         <v>2093</v>
       </c>
       <c r="W606" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA606" t="b">
         <v>0</v>
@@ -48330,7 +48333,7 @@
         <v>2094</v>
       </c>
       <c r="W607" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA607" t="b">
         <v>0</v>
@@ -48398,7 +48401,7 @@
         <v>2095</v>
       </c>
       <c r="W608" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA608" t="b">
         <v>0</v>
@@ -48466,7 +48469,7 @@
         <v>2096</v>
       </c>
       <c r="W609" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA609" t="b">
         <v>0</v>
@@ -48534,7 +48537,7 @@
         <v>2097</v>
       </c>
       <c r="W610" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA610" t="b">
         <v>0</v>
@@ -48602,7 +48605,7 @@
         <v>2098</v>
       </c>
       <c r="W611" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA611" t="b">
         <v>0</v>
@@ -48670,7 +48673,7 @@
         <v>2099</v>
       </c>
       <c r="W612" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA612" t="b">
         <v>0</v>
@@ -48738,7 +48741,7 @@
         <v>2100</v>
       </c>
       <c r="W613" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA613" t="b">
         <v>0</v>
@@ -48806,7 +48809,7 @@
         <v>2101</v>
       </c>
       <c r="W614" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA614" t="b">
         <v>0</v>
@@ -48874,7 +48877,7 @@
         <v>2102</v>
       </c>
       <c r="W615" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA615" t="b">
         <v>0</v>
@@ -48942,7 +48945,7 @@
         <v>2103</v>
       </c>
       <c r="W616" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA616" t="b">
         <v>0</v>
@@ -49010,7 +49013,7 @@
         <v>2103</v>
       </c>
       <c r="W617" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA617" t="b">
         <v>0</v>
@@ -49078,7 +49081,7 @@
         <v>2104</v>
       </c>
       <c r="W618" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA618" t="b">
         <v>0</v>
@@ -49146,7 +49149,7 @@
         <v>2105</v>
       </c>
       <c r="W619" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA619" t="b">
         <v>0</v>
@@ -49214,7 +49217,7 @@
         <v>2106</v>
       </c>
       <c r="W620" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA620" t="b">
         <v>0</v>
@@ -49282,7 +49285,7 @@
         <v>2107</v>
       </c>
       <c r="W621" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA621" t="b">
         <v>0</v>
@@ -49350,7 +49353,7 @@
         <v>2108</v>
       </c>
       <c r="W622" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA622" t="b">
         <v>0</v>
@@ -49382,7 +49385,7 @@
         <v>1349</v>
       </c>
       <c r="I623" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="J623" s="1">
         <v>46279</v>
@@ -49397,16 +49400,19 @@
         <v>1354</v>
       </c>
       <c r="N623" s="1">
-        <v>46312</v>
+        <v>46288</v>
       </c>
       <c r="O623" s="1">
         <v>46290</v>
       </c>
+      <c r="P623" t="s">
+        <v>1601</v>
+      </c>
       <c r="Q623">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="R623">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S623" t="s">
         <v>1613</v>
@@ -49418,13 +49424,13 @@
         <v>2109</v>
       </c>
       <c r="V623" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="W623" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA623" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624" spans="1:27">
@@ -49489,7 +49495,7 @@
         <v>2110</v>
       </c>
       <c r="W624" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA624" t="b">
         <v>0</v>
@@ -49538,9 +49544,6 @@
       <c r="N625" s="1">
         <v>46320</v>
       </c>
-      <c r="O625" s="1">
-        <v>46297</v>
-      </c>
       <c r="P625" t="s">
         <v>1599</v>
       </c>
@@ -49559,11 +49562,8 @@
       <c r="U625" t="s">
         <v>2111</v>
       </c>
-      <c r="V625" t="s">
-        <v>2127</v>
-      </c>
       <c r="W625" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA625" t="b">
         <v>0</v>
@@ -49631,7 +49631,7 @@
         <v>2112</v>
       </c>
       <c r="W626" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA626" t="b">
         <v>0</v>
@@ -49684,10 +49684,10 @@
         <v>46304</v>
       </c>
       <c r="Q627">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R627">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S627" t="s">
         <v>1613</v>
@@ -49702,7 +49702,7 @@
         <v>2128</v>
       </c>
       <c r="W627" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA627" t="b">
         <v>1</v>
@@ -49755,10 +49755,10 @@
         <v>46304</v>
       </c>
       <c r="Q628">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R628">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S628" t="s">
         <v>1613</v>
@@ -49773,7 +49773,7 @@
         <v>2128</v>
       </c>
       <c r="W628" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA628" t="b">
         <v>1</v>
@@ -49841,7 +49841,7 @@
         <v>2114</v>
       </c>
       <c r="W629" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA629" t="b">
         <v>0</v>
@@ -49909,7 +49909,7 @@
         <v>2115</v>
       </c>
       <c r="W630" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA630" t="b">
         <v>0</v>
@@ -49977,7 +49977,7 @@
         <v>2116</v>
       </c>
       <c r="W631" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA631" t="b">
         <v>0</v>
@@ -50006,7 +50006,7 @@
         <v>2721</v>
       </c>
       <c r="H632" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I632" t="s">
         <v>1352</v>
@@ -50029,11 +50029,14 @@
       <c r="O632" s="1">
         <v>46297</v>
       </c>
+      <c r="P632" t="s">
+        <v>1612</v>
+      </c>
       <c r="Q632">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R632">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S632" t="s">
         <v>1613</v>
@@ -50048,10 +50051,10 @@
         <v>2129</v>
       </c>
       <c r="W632" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA632" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="633" spans="1:27">
@@ -50116,7 +50119,7 @@
         <v>2118</v>
       </c>
       <c r="W633" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA633" t="b">
         <v>0</v>
@@ -50184,7 +50187,7 @@
         <v>2119</v>
       </c>
       <c r="W634" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA634" t="b">
         <v>0</v>
@@ -50237,10 +50240,10 @@
         <v>46326</v>
       </c>
       <c r="Q635">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R635">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S635" t="s">
         <v>1613</v>
@@ -50252,7 +50255,7 @@
         <v>2130</v>
       </c>
       <c r="W635" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA635" t="b">
         <v>1</v>
@@ -50305,10 +50308,10 @@
         <v>46326</v>
       </c>
       <c r="Q636">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R636">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S636" t="s">
         <v>1613</v>
@@ -50320,7 +50323,7 @@
         <v>2131</v>
       </c>
       <c r="W636" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA636" t="b">
         <v>1</v>
@@ -50388,7 +50391,7 @@
         <v>2120</v>
       </c>
       <c r="W637" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA637" t="b">
         <v>0</v>
@@ -50438,10 +50441,10 @@
         <v>46327</v>
       </c>
       <c r="Q638">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S638" t="s">
         <v>1613</v>
@@ -50449,8 +50452,11 @@
       <c r="T638" t="s">
         <v>1613</v>
       </c>
+      <c r="V638" t="s">
+        <v>2132</v>
+      </c>
       <c r="W638" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA638" t="b">
         <v>1</v>
@@ -50518,7 +50524,7 @@
         <v>2121</v>
       </c>
       <c r="W639" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA639" t="b">
         <v>0</v>
@@ -50586,7 +50592,7 @@
         <v>2121</v>
       </c>
       <c r="W640" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA640" t="b">
         <v>0</v>
@@ -50654,7 +50660,7 @@
         <v>2121</v>
       </c>
       <c r="W641" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA641" t="b">
         <v>0</v>
@@ -50707,10 +50713,10 @@
         <v>46308</v>
       </c>
       <c r="Q642">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R642">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S642" t="s">
         <v>1613</v>
@@ -50719,10 +50725,10 @@
         <v>1613</v>
       </c>
       <c r="V642" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="W642" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA642" t="b">
         <v>1</v>
@@ -50771,9 +50777,6 @@
       <c r="N643" s="1">
         <v>46308</v>
       </c>
-      <c r="O643" s="1">
-        <v>46300</v>
-      </c>
       <c r="P643" t="s">
         <v>1610</v>
       </c>
@@ -50792,11 +50795,8 @@
       <c r="U643" t="s">
         <v>2122</v>
       </c>
-      <c r="V643" t="s">
-        <v>2133</v>
-      </c>
       <c r="W643" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA643" t="b">
         <v>0</v>
@@ -50864,7 +50864,7 @@
         <v>2123</v>
       </c>
       <c r="W644" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA644" t="b">
         <v>0</v>
@@ -50932,7 +50932,7 @@
         <v>2124</v>
       </c>
       <c r="W645" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA645" t="b">
         <v>0</v>
@@ -50982,10 +50982,10 @@
         <v>46333</v>
       </c>
       <c r="Q646">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R646">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S646" t="s">
         <v>1613</v>
@@ -50994,7 +50994,7 @@
         <v>1614</v>
       </c>
       <c r="W646" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA646" t="b">
         <v>1</v>
@@ -51044,10 +51044,10 @@
         <v>46313</v>
       </c>
       <c r="Q647">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S647" t="s">
         <v>1614</v>
@@ -51055,8 +51055,11 @@
       <c r="T647" t="s">
         <v>1614</v>
       </c>
+      <c r="U647" t="s">
+        <v>2125</v>
+      </c>
       <c r="W647" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA647" t="b">
         <v>1</v>
@@ -51106,10 +51109,10 @@
         <v>46333</v>
       </c>
       <c r="Q648">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R648">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S648" t="s">
         <v>1613</v>
@@ -51117,8 +51120,11 @@
       <c r="T648" t="s">
         <v>1613</v>
       </c>
+      <c r="V648" t="s">
+        <v>2134</v>
+      </c>
       <c r="W648" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA648" t="b">
         <v>1</v>
@@ -51168,10 +51174,10 @@
         <v>46313</v>
       </c>
       <c r="Q649">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S649" t="s">
         <v>1614</v>
@@ -51179,8 +51185,11 @@
       <c r="T649" t="s">
         <v>1614</v>
       </c>
+      <c r="U649" t="s">
+        <v>2125</v>
+      </c>
       <c r="W649" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA649" t="b">
         <v>1</v>
@@ -51230,10 +51239,10 @@
         <v>46313</v>
       </c>
       <c r="Q650">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R650">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S650" t="s">
         <v>1613</v>
@@ -51242,7 +51251,7 @@
         <v>1614</v>
       </c>
       <c r="W650" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA650" t="b">
         <v>1</v>
@@ -51292,10 +51301,10 @@
         <v>46313</v>
       </c>
       <c r="Q651">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R651">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S651" t="s">
         <v>1613</v>
@@ -51304,7 +51313,7 @@
         <v>1614</v>
       </c>
       <c r="W651" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA651" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -47840,10 +47840,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R599">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S599" t="s">
         <v>1635</v>
@@ -49484,10 +49484,10 @@
         <v>1623</v>
       </c>
       <c r="Q623">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R623">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="S623" t="s">
         <v>1635</v>
@@ -49759,10 +49759,10 @@
         <v>46304</v>
       </c>
       <c r="Q627">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R627">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S627" t="s">
         <v>1635</v>
@@ -49830,10 +49830,10 @@
         <v>46304</v>
       </c>
       <c r="Q628">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R628">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S628" t="s">
         <v>1635</v>
@@ -50315,10 +50315,10 @@
         <v>46326</v>
       </c>
       <c r="Q635">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="R635">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S635" t="s">
         <v>1635</v>
@@ -50383,10 +50383,10 @@
         <v>46326</v>
       </c>
       <c r="Q636">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="R636">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S636" t="s">
         <v>1635</v>
@@ -50516,10 +50516,10 @@
         <v>46327</v>
       </c>
       <c r="Q638">
-        <v>-23</v>
+        <v>-20</v>
       </c>
       <c r="R638">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S638" t="s">
         <v>1635</v>
@@ -50788,10 +50788,10 @@
         <v>46308</v>
       </c>
       <c r="Q642">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="R642">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S642" t="s">
         <v>1635</v>
@@ -51057,10 +51057,10 @@
         <v>46333</v>
       </c>
       <c r="Q646">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R646">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S646" t="s">
         <v>1635</v>
@@ -51119,10 +51119,10 @@
         <v>46333</v>
       </c>
       <c r="Q647">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R647">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S647" t="s">
         <v>1636</v>
@@ -51184,10 +51184,10 @@
         <v>46333</v>
       </c>
       <c r="Q648">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R648">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S648" t="s">
         <v>1635</v>
@@ -51249,10 +51249,10 @@
         <v>46309</v>
       </c>
       <c r="Q649">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="R649">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S649" t="s">
         <v>1636</v>
@@ -51314,10 +51314,10 @@
         <v>46333</v>
       </c>
       <c r="Q650">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R650">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S650" t="s">
         <v>1635</v>
@@ -51376,10 +51376,10 @@
         <v>46313</v>
       </c>
       <c r="Q651">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R651">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S651" t="s">
         <v>1635</v>
@@ -51438,10 +51438,10 @@
         <v>46315</v>
       </c>
       <c r="Q652">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R652">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S652" t="s">
         <v>1635</v>
@@ -51500,10 +51500,10 @@
         <v>46311</v>
       </c>
       <c r="Q653">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R653">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S653" t="s">
         <v>1635</v>
@@ -51562,10 +51562,10 @@
         <v>46311</v>
       </c>
       <c r="Q654">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R654">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S654" t="s">
         <v>1635</v>
@@ -51624,10 +51624,10 @@
         <v>46315</v>
       </c>
       <c r="Q655">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R655">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S655" t="s">
         <v>1635</v>
@@ -51686,10 +51686,10 @@
         <v>46311</v>
       </c>
       <c r="Q656">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R656">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S656" t="s">
         <v>1635</v>
@@ -51748,10 +51748,10 @@
         <v>46311</v>
       </c>
       <c r="Q657">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R657">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S657" t="s">
         <v>1635</v>
@@ -51810,10 +51810,10 @@
         <v>46311</v>
       </c>
       <c r="Q658">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R658">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S658" t="s">
         <v>1636</v>
@@ -51875,10 +51875,10 @@
         <v>46311</v>
       </c>
       <c r="Q659">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R659">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S659" t="s">
         <v>1635</v>
@@ -51937,10 +51937,10 @@
         <v>46311</v>
       </c>
       <c r="Q660">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R660">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S660" t="s">
         <v>1636</v>
@@ -52002,10 +52002,10 @@
         <v>46311</v>
       </c>
       <c r="Q661">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R661">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S661" t="s">
         <v>1636</v>
@@ -52064,10 +52064,10 @@
         <v>46311</v>
       </c>
       <c r="Q662">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R662">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S662" t="s">
         <v>1636</v>
@@ -52129,10 +52129,10 @@
         <v>46311</v>
       </c>
       <c r="Q663">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R663">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S663" t="s">
         <v>1635</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -6508,7 +6508,7 @@
     <t>Operador pediu para fornecer o PN informado. Godoy 18/09/26. AWB 12758218764 -  volume retirado na loja GOLLOG - NAT por teodoro silva no dia 21/09. Godoy 22/09/26.  Item atendido pela NF 2227 em 22/09/2026. Godoy 24/09/2026.</t>
   </si>
   <si>
-    <t>AWB 12759588944 - volume retirado na loja GOLLOG - NAT por teodoro silva em 25/09. Godoy 06/10/26. Informado recibo 822/FAB/26 porém PN atendido não consta como alternado do PN em emergência. Ramon 08/10/26.</t>
+    <t>AWB 12759588944 - volume retirado na loja GOLLOG - NAT por teodoro silva em 25/09. Godoy 06/10/26. Informado recibo 822/FAB/26 porém PN atendido não consta como alternado do PN em emergência. Ramon 08/10/26. Alternância comprovada e cadastrada no SILOMS. Ramon 22/10/26.</t>
   </si>
   <si>
     <t>será atendido pelo estoque FAB pedido n° 18422910. Godoy 16/09/26</t>
@@ -48029,10 +48029,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R599">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="S599" t="s">
         <v>1668</v>
@@ -49646,7 +49646,7 @@
         <v>2702</v>
       </c>
       <c r="H623" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="I623" t="s">
         <v>1401</v>
@@ -49673,10 +49673,10 @@
         <v>1650</v>
       </c>
       <c r="Q623">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="R623">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="S623" t="s">
         <v>1668</v>
@@ -50492,10 +50492,10 @@
         <v>46326</v>
       </c>
       <c r="Q635">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R635">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S635" t="s">
         <v>1668</v>
@@ -50560,10 +50560,10 @@
         <v>46305</v>
       </c>
       <c r="Q636">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R636">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S636" t="s">
         <v>1668</v>
@@ -50696,10 +50696,10 @@
         <v>46327</v>
       </c>
       <c r="Q638">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R638">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S638" t="s">
         <v>1668</v>
@@ -51243,10 +51243,10 @@
         <v>46214</v>
       </c>
       <c r="Q646">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R646">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S646" t="s">
         <v>1668</v>
@@ -51379,10 +51379,10 @@
         <v>46214</v>
       </c>
       <c r="Q648">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R648">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S648" t="s">
         <v>1668</v>
@@ -51518,10 +51518,10 @@
         <v>1663</v>
       </c>
       <c r="Q650">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R650">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S650" t="s">
         <v>1668</v>
@@ -51592,10 +51592,10 @@
         <v>1663</v>
       </c>
       <c r="Q651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R651">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S651" t="s">
         <v>1668</v>
@@ -51660,10 +51660,10 @@
         <v>46311</v>
       </c>
       <c r="Q652">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R652">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S652" t="s">
         <v>1668</v>
@@ -51864,10 +51864,10 @@
         <v>46310</v>
       </c>
       <c r="Q655">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R655">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S655" t="s">
         <v>1668</v>
@@ -52488,10 +52488,10 @@
         <v>46316</v>
       </c>
       <c r="Q664">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R664">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S664" t="s">
         <v>1668</v>
@@ -52553,10 +52553,10 @@
         <v>46316</v>
       </c>
       <c r="Q665">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R665">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S665" t="s">
         <v>1668</v>
@@ -52621,10 +52621,10 @@
         <v>46316</v>
       </c>
       <c r="Q666">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R666">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S666" t="s">
         <v>1668</v>
@@ -52686,10 +52686,10 @@
         <v>46340</v>
       </c>
       <c r="Q667">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R667">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S667" t="s">
         <v>1668</v>
@@ -52754,10 +52754,10 @@
         <v>46327</v>
       </c>
       <c r="Q668">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R668">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T668" t="s">
         <v>1669</v>
@@ -52816,10 +52816,10 @@
         <v>46322</v>
       </c>
       <c r="Q669">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R669">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S669" t="s">
         <v>1668</v>
@@ -52881,10 +52881,10 @@
         <v>46322</v>
       </c>
       <c r="Q670">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R670">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S670" t="s">
         <v>1668</v>
@@ -52949,10 +52949,10 @@
         <v>46346</v>
       </c>
       <c r="Q671">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R671">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S671" t="s">
         <v>1668</v>
@@ -53011,10 +53011,10 @@
         <v>46346</v>
       </c>
       <c r="Q672">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R672">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S672" t="s">
         <v>1668</v>
@@ -53073,10 +53073,10 @@
         <v>46326</v>
       </c>
       <c r="Q673">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R673">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S673" t="s">
         <v>1668</v>
@@ -53135,10 +53135,10 @@
         <v>46326</v>
       </c>
       <c r="Q674">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R674">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S674" t="s">
         <v>1668</v>
@@ -53203,10 +53203,10 @@
         <v>46346</v>
       </c>
       <c r="Q675">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R675">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S675" t="s">
         <v>1668</v>
@@ -53271,10 +53271,10 @@
         <v>46346</v>
       </c>
       <c r="Q676">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R676">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S676" t="s">
         <v>1668</v>
@@ -53339,10 +53339,10 @@
         <v>46326</v>
       </c>
       <c r="Q677">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R677">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S677" t="s">
         <v>1669</v>
@@ -53407,10 +53407,10 @@
         <v>46323</v>
       </c>
       <c r="Q678">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R678">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S678" t="s">
         <v>1668</v>
@@ -53469,10 +53469,10 @@
         <v>46324</v>
       </c>
       <c r="Q679">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R679">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S679" t="s">
         <v>1668</v>
@@ -53531,10 +53531,10 @@
         <v>46324</v>
       </c>
       <c r="Q680">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R680">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S680" t="s">
         <v>1669</v>
